--- a/Salary_comp_1791284732.xlsx
+++ b/Salary_comp_1791284732.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W84"/>
+  <dimension ref="A1:Y84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,85 +453,95 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>تاريخ  العلاوة المستحق</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>تاريخ الترقية</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>الراتب الاسمي</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>الزوجية</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>الاطفال</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>المنصب</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>الشهادة</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>موقع جغرافي</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>مهنية</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>الهندسية</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>الخطورة</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>الاضافات</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>التقاعد</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>الضريبة</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>الاستقطاعات</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>الضمان الاجتماعي</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>المجموع.1</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>الصافي</t>
         </is>
@@ -562,55 +576,61 @@
           <t>سابعة</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>47088</v>
+      </c>
+      <c r="I2" t="n">
         <v>1030000</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>50000</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>10000</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>154500</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>463500</v>
       </c>
-      <c r="L2" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O2" t="n">
         <v>309000</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>2057000</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>103000</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>73633</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
         <v>2575</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>179208</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>1877792</v>
       </c>
     </row>
@@ -643,55 +663,61 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>47088</v>
+      </c>
+      <c r="I3" t="n">
         <v>600000</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>50000</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>20000</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>90000</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>150000</v>
       </c>
-      <c r="L3" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O3" t="n">
         <v>180000</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1130000</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>60000</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>38083</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
         <v>1500</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>99583</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>1030417</v>
       </c>
     </row>
@@ -724,55 +750,61 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>47088</v>
+      </c>
+      <c r="I4" t="n">
         <v>600000</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>50000</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>30000</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>90000</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>270000</v>
       </c>
-      <c r="L4" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>300000</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>1380000</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>60000</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>10583</v>
       </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
         <v>1500</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>72083</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>1307917</v>
       </c>
     </row>
@@ -805,55 +837,61 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>47088</v>
+      </c>
+      <c r="I5" t="n">
         <v>600000</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>90000</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>270000</v>
       </c>
-      <c r="L5" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O5" t="n">
         <v>180000</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>1180000</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>60000</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>43083</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>1500</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>104583</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>1075417</v>
       </c>
     </row>
@@ -886,55 +924,61 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>47088</v>
+      </c>
+      <c r="I6" t="n">
         <v>620000</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>50000</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>30000</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>93000</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>775000</v>
       </c>
-      <c r="L6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>310000</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>1918000</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>62000</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>38283</v>
       </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
         <v>1550</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>101833</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>1816167</v>
       </c>
     </row>
@@ -967,55 +1011,61 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>47088</v>
+      </c>
+      <c r="I7" t="n">
         <v>620000</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>93000</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>775000</v>
       </c>
-      <c r="L7" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O7" t="n">
         <v>186000</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>1714000</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>62000</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>45783</v>
       </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
         <v>1550</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>109333</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>1604667</v>
       </c>
     </row>
@@ -1048,55 +1098,61 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>47088</v>
+      </c>
+      <c r="I8" t="n">
         <v>620000</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>93000</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>775000</v>
       </c>
-      <c r="L8" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O8" t="n">
         <v>186000</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>1714000</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>62000</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>45783</v>
       </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
         <v>1550</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>109333</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>1604667</v>
       </c>
     </row>
@@ -1129,55 +1185,61 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>47088</v>
+      </c>
+      <c r="I9" t="n">
         <v>525000</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>50000</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>20000</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>78750</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>236250</v>
       </c>
-      <c r="L9" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>183750</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>1133750</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>52500</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>21938</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
         <v>1312.5</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>75750.5</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>1057999.5</v>
       </c>
     </row>
@@ -1210,55 +1272,61 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>47088</v>
+      </c>
+      <c r="I10" t="n">
         <v>533000</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>50000</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>20000</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>79950</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>239850</v>
       </c>
-      <c r="L10" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O10" t="n">
         <v>159900</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>1122700</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>53300</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>29308</v>
       </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
         <v>1332.5</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>83940.5</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>1038759.5</v>
       </c>
     </row>
@@ -1291,55 +1359,61 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>47088</v>
+      </c>
+      <c r="I11" t="n">
         <v>435000</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>50000</v>
       </c>
-      <c r="I11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>65250</v>
       </c>
-      <c r="L11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O11" t="n">
         <v>130500</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>760750</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>43500</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
         <v>1087.5</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>44587.5</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>716162.5</v>
       </c>
     </row>
@@ -1372,55 +1446,57 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
         <v>441000</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>198450</v>
       </c>
-      <c r="L12" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O12" t="n">
         <v>132300</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>811750</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>44100</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>21483</v>
       </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
         <v>1102.5</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>66685.5</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>745064.5</v>
       </c>
     </row>
@@ -1453,55 +1529,57 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
         <v>441000</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>50000</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>20000</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>198450</v>
       </c>
-      <c r="L13" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O13" t="n">
         <v>132300</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>881750</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>44100</v>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
         <v>1102.5</v>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
         <v>45202.5</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>836547.5</v>
       </c>
     </row>
@@ -1534,55 +1612,57 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
         <v>441000</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>198450</v>
       </c>
-      <c r="L14" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O14" t="n">
         <v>132300</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>811750</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>44100</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>21483</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>1102.5</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>66685.5</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>745064.5</v>
       </c>
     </row>
@@ -1615,55 +1695,57 @@
           <t>خامسة</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
         <v>453000</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>50000</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>20000</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>203850</v>
       </c>
-      <c r="L15" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>158550</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
       <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>925400</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>45300</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>35</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
         <v>1132.5</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>46467.5</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>878932.5</v>
       </c>
     </row>
@@ -1696,55 +1778,57 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
         <v>362000</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>50000</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>10000</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>162900</v>
       </c>
-      <c r="L16" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O16" t="n">
         <v>108600</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>733500</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>36200</v>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
         <v>905</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>37105</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>696395</v>
       </c>
     </row>
@@ -1777,27 +1861,23 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
         <v>362000</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>50000</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>20000</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>54300</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -1808,24 +1888,30 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>486300</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>36200</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
       <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
         <v>905</v>
       </c>
-      <c r="V17" t="n">
+      <c r="X17" t="n">
         <v>37105</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>449195</v>
       </c>
     </row>
@@ -1858,55 +1944,57 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
         <v>362000</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>50000</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>10000</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>162900</v>
       </c>
-      <c r="L18" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>126700</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>751600</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>36200</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>8183</v>
       </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
         <v>905</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>45288</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>706312</v>
       </c>
     </row>
@@ -1939,55 +2027,57 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
         <v>368000</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>50000</v>
       </c>
-      <c r="I19" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>55200</v>
       </c>
-      <c r="L19" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>43750</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>596950</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>36800</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
         <v>920</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>37720</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>559230</v>
       </c>
     </row>
@@ -2020,55 +2110,57 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
         <v>374000</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>50000</v>
       </c>
-      <c r="I20" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L20" t="n">
         <v>56100</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>56100</v>
       </c>
-      <c r="L20" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O20" t="n">
         <v>112200</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>728400</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>37400</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
         <v>935</v>
       </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
         <v>38335</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
         <v>690065</v>
       </c>
     </row>
@@ -2101,55 +2193,57 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
         <v>374000</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>50000</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>10000</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>56100</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>467500</v>
       </c>
-      <c r="L21" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O21" t="n">
         <v>112200</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>1109800</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>37400</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>10208</v>
       </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
         <v>935</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>48543</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>1061257</v>
       </c>
     </row>
@@ -2182,55 +2276,57 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
         <v>380000</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>171000</v>
       </c>
-      <c r="L22" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O22" t="n">
         <v>114000</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>705000</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>38000</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>13383</v>
       </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>950</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>52333</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>652667</v>
       </c>
     </row>
@@ -2263,55 +2359,57 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
         <v>380000</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>171000</v>
       </c>
-      <c r="L23" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O23" t="n">
         <v>114000</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>705000</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>38000</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>13383</v>
       </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
         <v>950</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>52333</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>652667</v>
       </c>
     </row>
@@ -2344,27 +2442,23 @@
           <t>سادسة</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
         <v>392000</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>490000</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -2375,24 +2469,30 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>882000</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>39200</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>14733</v>
       </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
         <v>980</v>
       </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
         <v>54913</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>827087</v>
       </c>
     </row>
@@ -2425,55 +2525,57 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
         <v>296000</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>44400</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>133200</v>
       </c>
-      <c r="L25" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>103600</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
       <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>617200</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>29600</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>3217</v>
       </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
         <v>740</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>33557</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>583643</v>
       </c>
     </row>
@@ -2506,55 +2608,57 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
         <v>308000</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>50000</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>20000</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>107800</v>
       </c>
-      <c r="L26" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O26" t="n">
         <v>92400</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>618200</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>30800</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>1450</v>
       </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
         <v>770</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>33020</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>585180</v>
       </c>
     </row>
@@ -2587,55 +2691,57 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
         <v>308000</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>50000</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>10000</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>107800</v>
       </c>
-      <c r="L27" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O27" t="n">
         <v>92400</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>608200</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>30800</v>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
       <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
         <v>770</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>31570</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>576630</v>
       </c>
     </row>
@@ -2668,55 +2774,57 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
         <v>308000</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>107800</v>
       </c>
-      <c r="L28" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O28" t="n">
         <v>92400</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>548200</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>30800</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>4561</v>
       </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
         <v>770</v>
       </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
         <v>36131</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>512069</v>
       </c>
     </row>
@@ -2749,55 +2857,57 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
         <v>308000</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>138600</v>
       </c>
-      <c r="L29" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O29" t="n">
         <v>77000</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>563600</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>30800</v>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
       <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
         <v>770</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>31570</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>532030</v>
       </c>
     </row>
@@ -2830,55 +2940,57 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
         <v>314000</v>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>47100</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>141300</v>
       </c>
-      <c r="L30" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O30" t="n">
         <v>94200</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>636600</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>31400</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>5017</v>
       </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
         <v>785</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>37202</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>599398</v>
       </c>
     </row>
@@ -2911,27 +3023,23 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
         <v>314000</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>50000</v>
       </c>
-      <c r="I31" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
       <c r="K31" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>141300</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -2942,24 +3050,30 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>545300</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>31400</v>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
       <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
         <v>785</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>32185</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>513115</v>
       </c>
     </row>
@@ -2992,55 +3106,57 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
         <v>314000</v>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>141300</v>
       </c>
-      <c r="L32" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O32" t="n">
         <v>94200</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>589500</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>31400</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>5017</v>
       </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
         <v>785</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>37202</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>552298</v>
       </c>
     </row>
@@ -3073,55 +3189,57 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
         <v>314000</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>50000</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>30000</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>141300</v>
       </c>
-      <c r="L33" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O33" t="n">
         <v>94200</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>669500</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>31400</v>
       </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
       <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
         <v>785</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>32185</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>637315</v>
       </c>
     </row>
@@ -3154,55 +3272,57 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G34" t="n">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
         <v>314000</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>50000</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>20000</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>141300</v>
       </c>
-      <c r="L34" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
       <c r="N34" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>109900</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
       <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>675200</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>31400</v>
       </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
       <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
         <v>785</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>32185</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
         <v>643015</v>
       </c>
     </row>
@@ -3235,55 +3355,57 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
         <v>314000</v>
       </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>141300</v>
       </c>
-      <c r="L35" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O35" t="n">
         <v>94200</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>589500</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>31400</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>5017</v>
       </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
         <v>785</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>37202</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>552298</v>
       </c>
     </row>
@@ -3316,55 +3438,57 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G36" t="n">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
         <v>314000</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>50000</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>30000</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>47100</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>141300</v>
       </c>
-      <c r="L36" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O36" t="n">
         <v>78500</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>700900</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>31400</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
       <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
         <v>785</v>
       </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
         <v>32185</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Y36" t="n">
         <v>668715</v>
       </c>
     </row>
@@ -3397,55 +3521,57 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
         <v>260000</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>39000</v>
       </c>
-      <c r="L37" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O37" t="n">
         <v>130000</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>469000</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>26000</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>867</v>
       </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
         <v>650</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>27517</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>441483</v>
       </c>
     </row>
@@ -3478,55 +3604,57 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
         <v>263000</v>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>39450</v>
       </c>
-      <c r="L38" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O38" t="n">
         <v>131500</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>473950</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>26300</v>
       </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
       <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
         <v>657.5</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>26957.5</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Y38" t="n">
         <v>446992.5</v>
       </c>
     </row>
@@ -3559,55 +3687,57 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
         <v>263000</v>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>65750</v>
       </c>
-      <c r="L39" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O39" t="n">
         <v>131500</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>500250</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>26300</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>1492</v>
       </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
         <v>657.5</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>28449.5</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>471800.5</v>
       </c>
     </row>
@@ -3640,55 +3770,57 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
         <v>269000</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>50000</v>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
       <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>67250</v>
       </c>
-      <c r="L40" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O40" t="n">
         <v>134500</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
         <v>560750</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>26900</v>
       </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
       <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
         <v>672.5</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>27572.5</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>533177.5</v>
       </c>
     </row>
@@ -3721,55 +3853,57 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
         <v>269000</v>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>50000</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>10000</v>
       </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>67250</v>
       </c>
-      <c r="L41" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O41" t="n">
         <v>134500</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
         <v>570750</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>26900</v>
       </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
       <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
         <v>672.5</v>
       </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
         <v>27572.5</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Y41" t="n">
         <v>543177.5</v>
       </c>
     </row>
@@ -3802,55 +3936,57 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
         <v>269000</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>67250</v>
       </c>
-      <c r="L42" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O42" t="n">
         <v>134500</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
         <v>510750</v>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>26900</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>1317</v>
       </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
         <v>672.5</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>28889.5</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Y42" t="n">
         <v>481860.5</v>
       </c>
     </row>
@@ -3883,57 +4019,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
         <v>213000</v>
       </c>
-      <c r="H43" t="n">
+      <c r="J43" t="n">
         <v>50000</v>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>31950</v>
       </c>
-      <c r="L43" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O43" t="n">
         <v>106500</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>441450</v>
       </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>21300</v>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
         <v>532.5</v>
       </c>
-      <c r="V43" t="n">
+      <c r="X43" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W43" t="n">
+      <c r="Y43" t="n">
         <v>419617.5</v>
       </c>
     </row>
@@ -3966,57 +4104,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
         <v>213000</v>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>50000</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>20000</v>
       </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>31950</v>
       </c>
-      <c r="L44" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O44" t="n">
         <v>106500</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
         <v>461450</v>
       </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
         <v>21300</v>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
         <v>532.5</v>
       </c>
-      <c r="V44" t="n">
+      <c r="X44" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Y44" t="n">
         <v>439617.5</v>
       </c>
     </row>
@@ -4049,57 +4189,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
         <v>213000</v>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>50000</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>10000</v>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>31950</v>
       </c>
-      <c r="L45" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O45" t="n">
         <v>106500</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
       <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
         <v>451450</v>
       </c>
-      <c r="R45" t="n">
+      <c r="T45" t="n">
         <v>21300</v>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
         <v>532.5</v>
       </c>
-      <c r="V45" t="n">
+      <c r="X45" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Y45" t="n">
         <v>429617.5</v>
       </c>
     </row>
@@ -4132,57 +4274,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
         <v>213000</v>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>31950</v>
       </c>
-      <c r="L46" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O46" t="n">
         <v>106500</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
         <v>391450</v>
       </c>
-      <c r="R46" t="n">
+      <c r="T46" t="n">
         <v>21300</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
         <v>532.5</v>
       </c>
-      <c r="V46" t="n">
+      <c r="X46" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W46" t="n">
+      <c r="Y46" t="n">
         <v>369617.5</v>
       </c>
     </row>
@@ -4215,57 +4359,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
         <v>213000</v>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>50000</v>
       </c>
-      <c r="I47" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
       <c r="K47" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>31950</v>
       </c>
-      <c r="L47" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O47" t="n">
         <v>106500</v>
       </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
         <v>481450</v>
       </c>
-      <c r="R47" t="n">
+      <c r="T47" t="n">
         <v>21300</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
         <v>532.5</v>
       </c>
-      <c r="V47" t="n">
+      <c r="X47" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W47" t="n">
+      <c r="Y47" t="n">
         <v>459617.5</v>
       </c>
     </row>
@@ -4298,57 +4444,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
         <v>213000</v>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>50000</v>
       </c>
-      <c r="I48" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
       <c r="K48" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
         <v>31950</v>
       </c>
-      <c r="L48" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O48" t="n">
         <v>106500</v>
       </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>481450</v>
       </c>
-      <c r="R48" t="n">
+      <c r="T48" t="n">
         <v>21300</v>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
         <v>532.5</v>
       </c>
-      <c r="V48" t="n">
+      <c r="X48" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W48" t="n">
+      <c r="Y48" t="n">
         <v>459617.5</v>
       </c>
     </row>
@@ -4381,57 +4529,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
         <v>213000</v>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>50000</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>20000</v>
       </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>31950</v>
       </c>
-      <c r="L49" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O49" t="n">
         <v>106500</v>
       </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
         <v>461450</v>
       </c>
-      <c r="R49" t="n">
+      <c r="T49" t="n">
         <v>21300</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
         <v>532.5</v>
       </c>
-      <c r="V49" t="n">
+      <c r="X49" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W49" t="n">
+      <c r="Y49" t="n">
         <v>439617.5</v>
       </c>
     </row>
@@ -4464,57 +4614,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
         <v>213000</v>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>50000</v>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
       <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>31950</v>
       </c>
-      <c r="L50" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O50" t="n">
         <v>106500</v>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
         <v>441450</v>
       </c>
-      <c r="R50" t="n">
+      <c r="T50" t="n">
         <v>21300</v>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
         <v>532.5</v>
       </c>
-      <c r="V50" t="n">
+      <c r="X50" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W50" t="n">
+      <c r="Y50" t="n">
         <v>419617.5</v>
       </c>
     </row>
@@ -4547,57 +4699,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
         <v>213000</v>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>50000</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>30000</v>
       </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>31950</v>
       </c>
-      <c r="L51" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O51" t="n">
         <v>106500</v>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
         <v>471450</v>
       </c>
-      <c r="R51" t="n">
+      <c r="T51" t="n">
         <v>21300</v>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
         <v>532.5</v>
       </c>
-      <c r="V51" t="n">
+      <c r="X51" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W51" t="n">
+      <c r="Y51" t="n">
         <v>449617.5</v>
       </c>
     </row>
@@ -4630,57 +4784,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G52" t="n">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
         <v>213000</v>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>50000</v>
       </c>
-      <c r="I52" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
       <c r="K52" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
         <v>31950</v>
       </c>
-      <c r="L52" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O52" t="n">
         <v>106500</v>
       </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
         <v>481450</v>
       </c>
-      <c r="R52" t="n">
+      <c r="T52" t="n">
         <v>21300</v>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
         <v>532.5</v>
       </c>
-      <c r="V52" t="n">
+      <c r="X52" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W52" t="n">
+      <c r="Y52" t="n">
         <v>459617.5</v>
       </c>
     </row>
@@ -4713,57 +4869,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
         <v>213000</v>
       </c>
-      <c r="H53" t="n">
+      <c r="J53" t="n">
         <v>50000</v>
       </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
       <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>31950</v>
       </c>
-      <c r="L53" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O53" t="n">
         <v>106500</v>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
         <v>441450</v>
       </c>
-      <c r="R53" t="n">
+      <c r="T53" t="n">
         <v>21300</v>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T53" t="n">
+      <c r="V53" t="n">
         <v>73575</v>
       </c>
-      <c r="U53" t="n">
+      <c r="W53" t="n">
         <v>532.5</v>
       </c>
-      <c r="V53" t="n">
+      <c r="X53" t="n">
         <v>95407.5</v>
       </c>
-      <c r="W53" t="n">
+      <c r="Y53" t="n">
         <v>346042.5</v>
       </c>
     </row>
@@ -4796,57 +4954,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
         <v>213000</v>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>50000</v>
       </c>
-      <c r="I54" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
       <c r="K54" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
         <v>31950</v>
       </c>
-      <c r="L54" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O54" t="n">
         <v>106500</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
         <v>481450</v>
       </c>
-      <c r="R54" t="n">
+      <c r="T54" t="n">
         <v>21300</v>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
         <v>532.5</v>
       </c>
-      <c r="V54" t="n">
+      <c r="X54" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W54" t="n">
+      <c r="Y54" t="n">
         <v>459617.5</v>
       </c>
     </row>
@@ -4879,57 +5039,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
         <v>213000</v>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>50000</v>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
       <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
         <v>31950</v>
       </c>
-      <c r="L55" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O55" t="n">
         <v>106500</v>
       </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
         <v>441450</v>
       </c>
-      <c r="R55" t="n">
+      <c r="T55" t="n">
         <v>21300</v>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T55" t="n">
+      <c r="V55" t="n">
         <v>58860</v>
       </c>
-      <c r="U55" t="n">
+      <c r="W55" t="n">
         <v>532.5</v>
       </c>
-      <c r="V55" t="n">
+      <c r="X55" t="n">
         <v>80692.5</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Y55" t="n">
         <v>360757.5</v>
       </c>
     </row>
@@ -4962,57 +5124,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
         <v>213000</v>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
         <v>31950</v>
       </c>
-      <c r="L56" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O56" t="n">
         <v>106500</v>
       </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
         <v>391450</v>
       </c>
-      <c r="R56" t="n">
+      <c r="T56" t="n">
         <v>21300</v>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
         <v>532.5</v>
       </c>
-      <c r="V56" t="n">
+      <c r="X56" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W56" t="n">
+      <c r="Y56" t="n">
         <v>369617.5</v>
       </c>
     </row>
@@ -5045,57 +5209,59 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
         <v>213000</v>
       </c>
-      <c r="H57" t="n">
+      <c r="J57" t="n">
         <v>50000</v>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>20000</v>
       </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>31950</v>
       </c>
-      <c r="L57" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O57" t="n">
         <v>106500</v>
       </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
         <v>461450</v>
       </c>
-      <c r="R57" t="n">
+      <c r="T57" t="n">
         <v>21300</v>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
         <v>532.5</v>
       </c>
-      <c r="V57" t="n">
+      <c r="X57" t="n">
         <v>21832.5</v>
       </c>
-      <c r="W57" t="n">
+      <c r="Y57" t="n">
         <v>439617.5</v>
       </c>
     </row>
@@ -5128,57 +5294,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
         <v>219000</v>
       </c>
-      <c r="H58" t="n">
+      <c r="J58" t="n">
         <v>50000</v>
       </c>
-      <c r="I58" t="n">
+      <c r="K58" t="n">
         <v>20000</v>
       </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
         <v>32850</v>
       </c>
-      <c r="L58" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O58" t="n">
         <v>109500</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
         <v>471350</v>
       </c>
-      <c r="R58" t="n">
+      <c r="T58" t="n">
         <v>21900</v>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
         <v>547.5</v>
       </c>
-      <c r="V58" t="n">
+      <c r="X58" t="n">
         <v>22447.5</v>
       </c>
-      <c r="W58" t="n">
+      <c r="Y58" t="n">
         <v>448902.5</v>
       </c>
     </row>
@@ -5211,57 +5379,59 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
         <v>176000</v>
       </c>
-      <c r="H59" t="n">
+      <c r="J59" t="n">
         <v>50000</v>
       </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
       <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
         <v>26400</v>
       </c>
-      <c r="L59" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O59" t="n">
         <v>88000</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
         <v>380400</v>
       </c>
-      <c r="R59" t="n">
+      <c r="T59" t="n">
         <v>17600</v>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T59" t="n">
+      <c r="V59" t="n">
         <v>38040</v>
       </c>
-      <c r="U59" t="n">
+      <c r="W59" t="n">
         <v>440</v>
       </c>
-      <c r="V59" t="n">
+      <c r="X59" t="n">
         <v>56080</v>
       </c>
-      <c r="W59" t="n">
+      <c r="Y59" t="n">
         <v>324320</v>
       </c>
     </row>
@@ -5294,57 +5464,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G60" t="n">
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
         <v>179000</v>
       </c>
-      <c r="H60" t="n">
+      <c r="J60" t="n">
         <v>50000</v>
       </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
       <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
         <v>26850</v>
       </c>
-      <c r="L60" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O60" t="n">
         <v>89500</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
         <v>385350</v>
       </c>
-      <c r="R60" t="n">
+      <c r="T60" t="n">
         <v>17900</v>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T60" t="n">
+      <c r="V60" t="n">
         <v>64225</v>
       </c>
-      <c r="U60" t="n">
+      <c r="W60" t="n">
         <v>447.5</v>
       </c>
-      <c r="V60" t="n">
+      <c r="X60" t="n">
         <v>82572.5</v>
       </c>
-      <c r="W60" t="n">
+      <c r="Y60" t="n">
         <v>302777.5</v>
       </c>
     </row>
@@ -5377,57 +5549,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
         <v>179000</v>
       </c>
-      <c r="H61" t="n">
+      <c r="J61" t="n">
         <v>50000</v>
       </c>
-      <c r="I61" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
       <c r="K61" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
         <v>26850</v>
       </c>
-      <c r="L61" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O61" t="n">
         <v>89500</v>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
         <v>425350</v>
       </c>
-      <c r="R61" t="n">
+      <c r="T61" t="n">
         <v>17900</v>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
         <v>447.5</v>
       </c>
-      <c r="V61" t="n">
+      <c r="X61" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W61" t="n">
+      <c r="Y61" t="n">
         <v>407002.5</v>
       </c>
     </row>
@@ -5460,57 +5634,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G62" t="n">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
         <v>179000</v>
       </c>
-      <c r="H62" t="n">
+      <c r="J62" t="n">
         <v>50000</v>
       </c>
-      <c r="I62" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
       <c r="K62" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
         <v>26850</v>
       </c>
-      <c r="L62" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O62" t="n">
         <v>89500</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
         <v>425350</v>
       </c>
-      <c r="R62" t="n">
+      <c r="T62" t="n">
         <v>17900</v>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
         <v>447.5</v>
       </c>
-      <c r="V62" t="n">
+      <c r="X62" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W62" t="n">
+      <c r="Y62" t="n">
         <v>407002.5</v>
       </c>
     </row>
@@ -5543,57 +5719,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G63" t="n">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="n">
         <v>179000</v>
       </c>
-      <c r="H63" t="n">
+      <c r="J63" t="n">
         <v>50000</v>
       </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>20000</v>
       </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
         <v>26850</v>
       </c>
-      <c r="L63" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O63" t="n">
         <v>89500</v>
       </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
         <v>405350</v>
       </c>
-      <c r="R63" t="n">
+      <c r="T63" t="n">
         <v>17900</v>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
         <v>447.5</v>
       </c>
-      <c r="V63" t="n">
+      <c r="X63" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W63" t="n">
+      <c r="Y63" t="n">
         <v>387002.5</v>
       </c>
     </row>
@@ -5626,57 +5804,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G64" t="n">
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
         <v>179000</v>
       </c>
-      <c r="H64" t="n">
+      <c r="J64" t="n">
         <v>50000</v>
       </c>
-      <c r="I64" t="n">
+      <c r="K64" t="n">
         <v>30000</v>
       </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
         <v>26850</v>
       </c>
-      <c r="L64" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O64" t="n">
         <v>89500</v>
       </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
         <v>415350</v>
       </c>
-      <c r="R64" t="n">
+      <c r="T64" t="n">
         <v>17900</v>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
         <v>447.5</v>
       </c>
-      <c r="V64" t="n">
+      <c r="X64" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W64" t="n">
+      <c r="Y64" t="n">
         <v>397002.5</v>
       </c>
     </row>
@@ -5709,57 +5889,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G65" t="n">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
         <v>179000</v>
       </c>
-      <c r="H65" t="n">
+      <c r="J65" t="n">
         <v>50000</v>
       </c>
-      <c r="I65" t="n">
+      <c r="K65" t="n">
         <v>30000</v>
       </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
         <v>26850</v>
       </c>
-      <c r="L65" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O65" t="n">
         <v>89500</v>
       </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
       <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
         <v>415350</v>
       </c>
-      <c r="R65" t="n">
+      <c r="T65" t="n">
         <v>17900</v>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
         <v>447.5</v>
       </c>
-      <c r="V65" t="n">
+      <c r="X65" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W65" t="n">
+      <c r="Y65" t="n">
         <v>397002.5</v>
       </c>
     </row>
@@ -5792,57 +5974,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G66" t="n">
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
         <v>179000</v>
       </c>
-      <c r="H66" t="n">
+      <c r="J66" t="n">
         <v>50000</v>
       </c>
-      <c r="I66" t="n">
+      <c r="K66" t="n">
         <v>20000</v>
       </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>26850</v>
       </c>
-      <c r="L66" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O66" t="n">
         <v>89500</v>
       </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
         <v>405350</v>
       </c>
-      <c r="R66" t="n">
+      <c r="T66" t="n">
         <v>17900</v>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
         <v>447.5</v>
       </c>
-      <c r="V66" t="n">
+      <c r="X66" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W66" t="n">
+      <c r="Y66" t="n">
         <v>387002.5</v>
       </c>
     </row>
@@ -5875,57 +6059,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G67" t="n">
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="n">
         <v>179000</v>
       </c>
-      <c r="H67" t="n">
+      <c r="J67" t="n">
         <v>50000</v>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
       <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
         <v>26850</v>
       </c>
-      <c r="L67" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O67" t="n">
         <v>89500</v>
       </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
       <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
         <v>385350</v>
       </c>
-      <c r="R67" t="n">
+      <c r="T67" t="n">
         <v>17900</v>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
         <v>447.5</v>
       </c>
-      <c r="V67" t="n">
+      <c r="X67" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W67" t="n">
+      <c r="Y67" t="n">
         <v>367002.5</v>
       </c>
     </row>
@@ -5958,57 +6144,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G68" t="n">
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
         <v>179000</v>
       </c>
-      <c r="H68" t="n">
+      <c r="J68" t="n">
         <v>50000</v>
       </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
       <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
         <v>26850</v>
       </c>
-      <c r="L68" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O68" t="n">
         <v>89500</v>
       </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
         <v>385350</v>
       </c>
-      <c r="R68" t="n">
+      <c r="T68" t="n">
         <v>17900</v>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
         <v>447.5</v>
       </c>
-      <c r="V68" t="n">
+      <c r="X68" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W68" t="n">
+      <c r="Y68" t="n">
         <v>367002.5</v>
       </c>
     </row>
@@ -6041,57 +6229,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G69" t="n">
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
         <v>179000</v>
       </c>
-      <c r="H69" t="n">
+      <c r="J69" t="n">
         <v>50000</v>
       </c>
-      <c r="I69" t="n">
+      <c r="K69" t="n">
         <v>10000</v>
       </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
         <v>26850</v>
       </c>
-      <c r="L69" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O69" t="n">
         <v>89500</v>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
         <v>395350</v>
       </c>
-      <c r="R69" t="n">
+      <c r="T69" t="n">
         <v>17900</v>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
         <v>447.5</v>
       </c>
-      <c r="V69" t="n">
+      <c r="X69" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W69" t="n">
+      <c r="Y69" t="n">
         <v>377002.5</v>
       </c>
     </row>
@@ -6124,57 +6314,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G70" t="n">
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
         <v>179000</v>
       </c>
-      <c r="H70" t="n">
+      <c r="J70" t="n">
         <v>50000</v>
       </c>
-      <c r="I70" t="n">
+      <c r="K70" t="n">
         <v>10000</v>
       </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
         <v>26850</v>
       </c>
-      <c r="L70" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O70" t="n">
         <v>89500</v>
       </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
         <v>395350</v>
       </c>
-      <c r="R70" t="n">
+      <c r="T70" t="n">
         <v>17900</v>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T70" t="n">
+      <c r="V70" t="n">
         <v>65891.667</v>
       </c>
-      <c r="U70" t="n">
+      <c r="W70" t="n">
         <v>447.5</v>
       </c>
-      <c r="V70" t="n">
+      <c r="X70" t="n">
         <v>84239.167</v>
       </c>
-      <c r="W70" t="n">
+      <c r="Y70" t="n">
         <v>311110.833</v>
       </c>
     </row>
@@ -6207,57 +6399,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G71" t="n">
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
         <v>179000</v>
       </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
         <v>26850</v>
       </c>
-      <c r="L71" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O71" t="n">
         <v>89500</v>
       </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
         <v>335350</v>
       </c>
-      <c r="R71" t="n">
+      <c r="T71" t="n">
         <v>17900</v>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
         <v>447.5</v>
       </c>
-      <c r="V71" t="n">
+      <c r="X71" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W71" t="n">
+      <c r="Y71" t="n">
         <v>317002.5</v>
       </c>
     </row>
@@ -6290,57 +6484,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
         <v>179000</v>
       </c>
-      <c r="H72" t="n">
+      <c r="J72" t="n">
         <v>50000</v>
       </c>
-      <c r="I72" t="n">
+      <c r="K72" t="n">
         <v>20000</v>
       </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
         <v>26850</v>
       </c>
-      <c r="L72" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O72" t="n">
         <v>89500</v>
       </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
       <c r="P72" t="n">
         <v>0</v>
       </c>
       <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
         <v>405350</v>
       </c>
-      <c r="R72" t="n">
+      <c r="T72" t="n">
         <v>17900</v>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
         <v>447.5</v>
       </c>
-      <c r="V72" t="n">
+      <c r="X72" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W72" t="n">
+      <c r="Y72" t="n">
         <v>387002.5</v>
       </c>
     </row>
@@ -6373,57 +6569,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G73" t="n">
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="n">
         <v>179000</v>
       </c>
-      <c r="H73" t="n">
+      <c r="J73" t="n">
         <v>50000</v>
       </c>
-      <c r="I73" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
       <c r="K73" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
         <v>26850</v>
       </c>
-      <c r="L73" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O73" t="n">
         <v>89500</v>
       </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
       <c r="P73" t="n">
         <v>0</v>
       </c>
       <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
         <v>425350</v>
       </c>
-      <c r="R73" t="n">
+      <c r="T73" t="n">
         <v>17900</v>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
         <v>447.5</v>
       </c>
-      <c r="V73" t="n">
+      <c r="X73" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W73" t="n">
+      <c r="Y73" t="n">
         <v>407002.5</v>
       </c>
     </row>
@@ -6456,57 +6654,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G74" t="n">
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="n">
         <v>179000</v>
       </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
         <v>26850</v>
       </c>
-      <c r="L74" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O74" t="n">
         <v>89500</v>
       </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
       <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
         <v>335350</v>
       </c>
-      <c r="R74" t="n">
+      <c r="T74" t="n">
         <v>17900</v>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="n">
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
         <v>447.5</v>
       </c>
-      <c r="V74" t="n">
+      <c r="X74" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W74" t="n">
+      <c r="Y74" t="n">
         <v>317002.5</v>
       </c>
     </row>
@@ -6539,57 +6739,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G75" t="n">
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
         <v>179000</v>
       </c>
-      <c r="H75" t="n">
+      <c r="J75" t="n">
         <v>50000</v>
       </c>
-      <c r="I75" t="n">
+      <c r="K75" t="n">
         <v>30000</v>
       </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
         <v>26850</v>
       </c>
-      <c r="L75" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M75" t="n">
+      <c r="N75" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O75" t="n">
         <v>89500</v>
       </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
       <c r="P75" t="n">
         <v>0</v>
       </c>
       <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
         <v>415350</v>
       </c>
-      <c r="R75" t="n">
+      <c r="T75" t="n">
         <v>17900</v>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
         <v>447.5</v>
       </c>
-      <c r="V75" t="n">
+      <c r="X75" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W75" t="n">
+      <c r="Y75" t="n">
         <v>397002.5</v>
       </c>
     </row>
@@ -6622,57 +6824,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G76" t="n">
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="n">
         <v>179000</v>
       </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
         <v>26850</v>
       </c>
-      <c r="L76" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M76" t="n">
+      <c r="N76" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O76" t="n">
         <v>89500</v>
       </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
       <c r="P76" t="n">
         <v>0</v>
       </c>
       <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
         <v>335350</v>
       </c>
-      <c r="R76" t="n">
+      <c r="T76" t="n">
         <v>17900</v>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
         <v>447.5</v>
       </c>
-      <c r="V76" t="n">
+      <c r="X76" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W76" t="n">
+      <c r="Y76" t="n">
         <v>317002.5</v>
       </c>
     </row>
@@ -6705,57 +6909,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G77" t="n">
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
         <v>179000</v>
       </c>
-      <c r="H77" t="n">
+      <c r="J77" t="n">
         <v>50000</v>
       </c>
-      <c r="I77" t="n">
+      <c r="K77" t="n">
         <v>10000</v>
       </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
         <v>26850</v>
       </c>
-      <c r="L77" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M77" t="n">
+      <c r="N77" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O77" t="n">
         <v>89500</v>
       </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
       <c r="P77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
         <v>395350</v>
       </c>
-      <c r="R77" t="n">
+      <c r="T77" t="n">
         <v>17900</v>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
         <v>447.5</v>
       </c>
-      <c r="V77" t="n">
+      <c r="X77" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W77" t="n">
+      <c r="Y77" t="n">
         <v>377002.5</v>
       </c>
     </row>
@@ -6788,57 +6994,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G78" t="n">
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="n">
         <v>179000</v>
       </c>
-      <c r="H78" t="n">
+      <c r="J78" t="n">
         <v>50000</v>
       </c>
-      <c r="I78" t="n">
+      <c r="K78" t="n">
         <v>20000</v>
       </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
         <v>26850</v>
       </c>
-      <c r="L78" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M78" t="n">
+      <c r="N78" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O78" t="n">
         <v>89500</v>
       </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
       <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
         <v>405350</v>
       </c>
-      <c r="R78" t="n">
+      <c r="T78" t="n">
         <v>17900</v>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
         <v>447.5</v>
       </c>
-      <c r="V78" t="n">
+      <c r="X78" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W78" t="n">
+      <c r="Y78" t="n">
         <v>387002.5</v>
       </c>
     </row>
@@ -6871,57 +7079,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G79" t="n">
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="n">
         <v>179000</v>
       </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
         <v>26850</v>
       </c>
-      <c r="L79" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M79" t="n">
+      <c r="N79" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O79" t="n">
         <v>89500</v>
       </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
         <v>335350</v>
       </c>
-      <c r="R79" t="n">
+      <c r="T79" t="n">
         <v>17900</v>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
         <v>447.5</v>
       </c>
-      <c r="V79" t="n">
+      <c r="X79" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W79" t="n">
+      <c r="Y79" t="n">
         <v>317002.5</v>
       </c>
     </row>
@@ -6954,57 +7164,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G80" t="n">
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="n">
         <v>179000</v>
       </c>
-      <c r="H80" t="n">
+      <c r="J80" t="n">
         <v>50000</v>
       </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
       <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
         <v>26850</v>
       </c>
-      <c r="L80" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M80" t="n">
+      <c r="N80" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O80" t="n">
         <v>89500</v>
       </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
       <c r="P80" t="n">
         <v>0</v>
       </c>
       <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
         <v>385350</v>
       </c>
-      <c r="R80" t="n">
+      <c r="T80" t="n">
         <v>17900</v>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
         <v>447.5</v>
       </c>
-      <c r="V80" t="n">
+      <c r="X80" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W80" t="n">
+      <c r="Y80" t="n">
         <v>367002.5</v>
       </c>
     </row>
@@ -7037,57 +7249,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G81" t="n">
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="n">
         <v>179000</v>
       </c>
-      <c r="H81" t="n">
+      <c r="J81" t="n">
         <v>50000</v>
       </c>
-      <c r="I81" t="n">
+      <c r="K81" t="n">
         <v>20000</v>
       </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
         <v>26850</v>
       </c>
-      <c r="L81" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M81" t="n">
+      <c r="N81" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O81" t="n">
         <v>89500</v>
       </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
       <c r="P81" t="n">
         <v>0</v>
       </c>
       <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
         <v>405350</v>
       </c>
-      <c r="R81" t="n">
+      <c r="T81" t="n">
         <v>17900</v>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
         <v>447.5</v>
       </c>
-      <c r="V81" t="n">
+      <c r="X81" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W81" t="n">
+      <c r="Y81" t="n">
         <v>387002.5</v>
       </c>
     </row>
@@ -7120,57 +7334,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G82" t="n">
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
         <v>179000</v>
       </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
         <v>26850</v>
       </c>
-      <c r="L82" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M82" t="n">
+      <c r="N82" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O82" t="n">
         <v>89500</v>
       </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
       <c r="P82" t="n">
         <v>0</v>
       </c>
       <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
         <v>335350</v>
       </c>
-      <c r="R82" t="n">
+      <c r="T82" t="n">
         <v>17900</v>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T82" t="n">
+      <c r="V82" t="n">
         <v>22356.667</v>
       </c>
-      <c r="U82" t="n">
+      <c r="W82" t="n">
         <v>447.5</v>
       </c>
-      <c r="V82" t="n">
+      <c r="X82" t="n">
         <v>40704.167</v>
       </c>
-      <c r="W82" t="n">
+      <c r="Y82" t="n">
         <v>294645.833</v>
       </c>
     </row>
@@ -7203,57 +7419,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G83" t="n">
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
         <v>179000</v>
       </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
         <v>26850</v>
       </c>
-      <c r="L83" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M83" t="n">
+      <c r="N83" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O83" t="n">
         <v>89500</v>
       </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
       <c r="P83" t="n">
         <v>0</v>
       </c>
       <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
         <v>335350</v>
       </c>
-      <c r="R83" t="n">
+      <c r="T83" t="n">
         <v>17900</v>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
         <v>447.5</v>
       </c>
-      <c r="V83" t="n">
+      <c r="X83" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W83" t="n">
+      <c r="Y83" t="n">
         <v>317002.5</v>
       </c>
     </row>
@@ -7284,57 +7502,59 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G84" t="n">
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="n">
         <v>179000</v>
       </c>
-      <c r="H84" t="n">
+      <c r="J84" t="n">
         <v>50000</v>
       </c>
-      <c r="I84" t="n">
-        <v>40000</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
       <c r="K84" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
         <v>26850</v>
       </c>
-      <c r="L84" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M84" t="n">
+      <c r="N84" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O84" t="n">
         <v>89500</v>
       </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
       <c r="P84" t="n">
         <v>0</v>
       </c>
       <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
         <v>425350</v>
       </c>
-      <c r="R84" t="n">
+      <c r="T84" t="n">
         <v>17900</v>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="T84" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" t="n">
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="n">
         <v>447.5</v>
       </c>
-      <c r="V84" t="n">
+      <c r="X84" t="n">
         <v>18347.5</v>
       </c>
-      <c r="W84" t="n">
+      <c r="Y84" t="n">
         <v>407002.5</v>
       </c>
     </row>

--- a/Salary_comp_1791284732.xlsx
+++ b/Salary_comp_1791284732.xlsx
@@ -1446,8 +1446,12 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I12" t="n">
         <v>441000</v>
       </c>
@@ -1529,8 +1533,12 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I13" t="n">
         <v>441000</v>
       </c>
@@ -1612,8 +1620,12 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I14" t="n">
         <v>441000</v>
       </c>
@@ -1695,8 +1707,12 @@
           <t>خامسة</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I15" t="n">
         <v>453000</v>
       </c>
@@ -1778,8 +1794,12 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I16" t="n">
         <v>362000</v>
       </c>
@@ -1861,8 +1881,12 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I17" t="n">
         <v>362000</v>
       </c>
@@ -1944,8 +1968,12 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I18" t="n">
         <v>362000</v>
       </c>
@@ -2027,8 +2055,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I19" t="n">
         <v>368000</v>
       </c>
@@ -2110,8 +2142,12 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I20" t="n">
         <v>374000</v>
       </c>
@@ -2193,8 +2229,12 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I21" t="n">
         <v>374000</v>
       </c>
@@ -2276,8 +2316,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I22" t="n">
         <v>380000</v>
       </c>
@@ -2359,8 +2403,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I23" t="n">
         <v>380000</v>
       </c>
@@ -2442,8 +2490,12 @@
           <t>سادسة</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I24" t="n">
         <v>392000</v>
       </c>
@@ -2525,8 +2577,12 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I25" t="n">
         <v>296000</v>
       </c>
@@ -2608,8 +2664,12 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I26" t="n">
         <v>308000</v>
       </c>
@@ -2691,8 +2751,12 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I27" t="n">
         <v>308000</v>
       </c>
@@ -2774,8 +2838,12 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I28" t="n">
         <v>308000</v>
       </c>
@@ -2857,8 +2925,12 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I29" t="n">
         <v>308000</v>
       </c>
@@ -2940,8 +3012,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I30" t="n">
         <v>314000</v>
       </c>
@@ -3023,8 +3099,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I31" t="n">
         <v>314000</v>
       </c>
@@ -3106,8 +3186,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I32" t="n">
         <v>314000</v>
       </c>
@@ -3189,8 +3273,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I33" t="n">
         <v>314000</v>
       </c>
@@ -3272,8 +3360,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I34" t="n">
         <v>314000</v>
       </c>
@@ -3355,8 +3447,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I35" t="n">
         <v>314000</v>
       </c>
@@ -3438,8 +3534,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I36" t="n">
         <v>314000</v>
       </c>
@@ -3521,8 +3621,12 @@
           <t>اولى</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I37" t="n">
         <v>260000</v>
       </c>
@@ -3604,8 +3708,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I38" t="n">
         <v>263000</v>
       </c>
@@ -3687,8 +3795,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I39" t="n">
         <v>263000</v>
       </c>
@@ -3770,8 +3882,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I40" t="n">
         <v>269000</v>
       </c>
@@ -3853,8 +3969,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I41" t="n">
         <v>269000</v>
       </c>
@@ -3936,8 +4056,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I42" t="n">
         <v>269000</v>
       </c>
@@ -4019,8 +4143,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I43" t="n">
         <v>213000</v>
       </c>
@@ -4104,8 +4232,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I44" t="n">
         <v>213000</v>
       </c>
@@ -4189,8 +4321,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I45" t="n">
         <v>213000</v>
       </c>
@@ -4274,8 +4410,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I46" t="n">
         <v>213000</v>
       </c>
@@ -4359,8 +4499,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I47" t="n">
         <v>213000</v>
       </c>
@@ -4444,8 +4588,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I48" t="n">
         <v>213000</v>
       </c>
@@ -4529,8 +4677,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I49" t="n">
         <v>213000</v>
       </c>
@@ -4614,8 +4766,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I50" t="n">
         <v>213000</v>
       </c>
@@ -4699,8 +4855,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I51" t="n">
         <v>213000</v>
       </c>
@@ -4784,8 +4944,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I52" t="n">
         <v>213000</v>
       </c>
@@ -4869,8 +5033,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I53" t="n">
         <v>213000</v>
       </c>
@@ -4954,8 +5122,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I54" t="n">
         <v>213000</v>
       </c>
@@ -5039,8 +5211,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I55" t="n">
         <v>213000</v>
       </c>
@@ -5124,8 +5300,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I56" t="n">
         <v>213000</v>
       </c>
@@ -5209,8 +5389,12 @@
           <t>ثانية</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I57" t="n">
         <v>213000</v>
       </c>
@@ -5294,8 +5478,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I58" t="n">
         <v>219000</v>
       </c>
@@ -5379,8 +5567,12 @@
           <t>ثالثة</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I59" t="n">
         <v>176000</v>
       </c>
@@ -5464,8 +5656,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I60" t="n">
         <v>179000</v>
       </c>
@@ -5549,8 +5745,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I61" t="n">
         <v>179000</v>
       </c>
@@ -5634,8 +5834,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H62" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I62" t="n">
         <v>179000</v>
       </c>
@@ -5719,8 +5923,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H63" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I63" t="n">
         <v>179000</v>
       </c>
@@ -5804,8 +6012,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I64" t="n">
         <v>179000</v>
       </c>
@@ -5889,8 +6101,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H65" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I65" t="n">
         <v>179000</v>
       </c>
@@ -5974,8 +6190,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I66" t="n">
         <v>179000</v>
       </c>
@@ -6059,8 +6279,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I67" t="n">
         <v>179000</v>
       </c>
@@ -6144,8 +6368,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I68" t="n">
         <v>179000</v>
       </c>
@@ -6229,8 +6457,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I69" t="n">
         <v>179000</v>
       </c>
@@ -6314,8 +6546,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H70" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I70" t="n">
         <v>179000</v>
       </c>
@@ -6399,8 +6635,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I71" t="n">
         <v>179000</v>
       </c>
@@ -6484,8 +6724,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I72" t="n">
         <v>179000</v>
       </c>
@@ -6569,8 +6813,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I73" t="n">
         <v>179000</v>
       </c>
@@ -6654,8 +6902,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H74" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I74" t="n">
         <v>179000</v>
       </c>
@@ -6739,8 +6991,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H75" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I75" t="n">
         <v>179000</v>
       </c>
@@ -6824,8 +7080,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H76" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I76" t="n">
         <v>179000</v>
       </c>
@@ -6909,8 +7169,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I77" t="n">
         <v>179000</v>
       </c>
@@ -6994,8 +7258,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I78" t="n">
         <v>179000</v>
       </c>
@@ -7079,8 +7347,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I79" t="n">
         <v>179000</v>
       </c>
@@ -7164,8 +7436,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I80" t="n">
         <v>179000</v>
       </c>
@@ -7249,8 +7525,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I81" t="n">
         <v>179000</v>
       </c>
@@ -7334,8 +7614,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I82" t="n">
         <v>179000</v>
       </c>
@@ -7419,8 +7703,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I83" t="n">
         <v>179000</v>
       </c>
@@ -7502,8 +7790,12 @@
           <t>رابعة</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>47088</v>
+      </c>
       <c r="I84" t="n">
         <v>179000</v>
       </c>

--- a/Salary_comp_1791284732.xlsx
+++ b/Salary_comp_1791284732.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>تاريخ  العلاوة المستحق</t>
+          <t>تاريخ العلاوة (السنوية)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
